--- a/public/user_import_example.xlsx
+++ b/public/user_import_example.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24990" windowHeight="11580"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>shop_name</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t>kkkk</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>2-User</t>
+  </si>
+  <si>
+    <t>3-sub  User</t>
   </si>
 </sst>
 </file>
@@ -726,7 +735,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1251,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="15.5714285714286" customWidth="1"/>
@@ -1263,6 +1272,7 @@
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="11.8571428571429" customWidth="1"/>
     <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="14.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1356,7 +1366,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1399,8 +1409,11 @@
       <c r="N3">
         <v>123456</v>
       </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1420,7 +1433,7 @@
         <v>17</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -1443,8 +1456,11 @@
       <c r="N4">
         <v>123456</v>
       </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1486,6 +1502,9 @@
       </c>
       <c r="N5">
         <v>123456</v>
+      </c>
+      <c r="S5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1508,7 +1527,7 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
